--- a/public/member list.xlsx
+++ b/public/member list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jgraf\renmotor_website_trial\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0593C79A-FAF2-4B92-8AD7-4F47FC748194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D821C84-AA5B-4B9E-9F2E-6E8537944161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" activeTab="1" xr2:uid="{63D0654A-77F0-4444-878E-EE1A2DF0A946}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{63D0654A-77F0-4444-878E-EE1A2DF0A946}"/>
   </bookViews>
   <sheets>
     <sheet name="Full Members" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="331">
   <si>
     <t>Joshua Levy</t>
   </si>
@@ -134,33 +134,6 @@
     <t>Louisa Ersenkal</t>
   </si>
   <si>
-    <t>ME</t>
-  </si>
-  <si>
-    <t>ME/AE</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>EE/CSE</t>
-  </si>
-  <si>
-    <t>DIS/COMMD</t>
-  </si>
-  <si>
-    <t>AE/ME</t>
-  </si>
-  <si>
-    <t>ME/DIS</t>
-  </si>
-  <si>
-    <t>ME Undergrad, MBA Grad</t>
-  </si>
-  <si>
     <t>Buisiness Lead</t>
   </si>
   <si>
@@ -176,24 +149,9 @@
     <t>Drivetrain Lead</t>
   </si>
   <si>
-    <t>ME = Mechanical Engineering</t>
-  </si>
-  <si>
-    <t>EE = Electrical Engineering</t>
-  </si>
-  <si>
-    <t>AE = Aeronautical/Aerospace engineering</t>
-  </si>
-  <si>
-    <t>DIS = Design Innovation and Society</t>
-  </si>
-  <si>
     <t>Materials Engineering &amp; Chemistry</t>
   </si>
   <si>
-    <t>CSE = Computer Science Engineering</t>
-  </si>
-  <si>
     <t>Brian Allen</t>
   </si>
   <si>
@@ -764,9 +722,6 @@
     <t>Ngai To Yu</t>
   </si>
   <si>
-    <t>COMMD = Communication, Media, and Design</t>
-  </si>
-  <si>
     <t>Vehicle Dynamics Lead</t>
   </si>
   <si>
@@ -806,9 +761,6 @@
     <t>Major</t>
   </si>
   <si>
-    <t>Major abbreviations</t>
-  </si>
-  <si>
     <t>Class of ___ year</t>
   </si>
   <si>
@@ -1050,6 +1002,33 @@
   </si>
   <si>
     <t>Atlas Copco</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering &amp; Design Innovation and Society</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering &amp; Master of Business Administration</t>
+  </si>
+  <si>
+    <t>Mechanical Engineering &amp;Design Innovation and Society</t>
+  </si>
+  <si>
+    <t>Aeronautical/Aerospace &amp; Mechanical Engineering</t>
+  </si>
+  <si>
+    <t>Design Innovation and Society &amp; Communication, Media, and Design</t>
+  </si>
+  <si>
+    <t>Aeronautical/Aerospace Engineering</t>
+  </si>
+  <si>
+    <t>Electrical &amp; Computer Science Engineering</t>
   </si>
 </sst>
 </file>
@@ -1412,289 +1391,268 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{405B87CB-CCE3-4456-9C71-BA4C1BAF669E}">
-  <dimension ref="B1:I33"/>
+  <dimension ref="B1:F33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="53.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C1" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="E1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D2">
         <v>2028</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="I2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>327</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
-      </c>
-      <c r="I3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="D4">
         <v>2028</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>329</v>
       </c>
       <c r="D5">
         <v>2028</v>
       </c>
       <c r="E5" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
-        <v>263</v>
-      </c>
-      <c r="I5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>330</v>
       </c>
       <c r="D6">
         <v>2028</v>
       </c>
       <c r="E6" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="F6" t="s">
-        <v>264</v>
-      </c>
-      <c r="I6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="D7">
         <v>2029</v>
       </c>
       <c r="F7" t="s">
-        <v>265</v>
-      </c>
-      <c r="I7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>327</v>
       </c>
       <c r="D8">
         <v>2028</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="F8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D9">
         <v>2028</v>
       </c>
       <c r="E9" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="F9" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D10">
         <v>2029</v>
       </c>
       <c r="E10" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="F10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>328</v>
       </c>
       <c r="D11">
         <v>2028</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D12">
         <v>2029</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>327</v>
       </c>
       <c r="D13">
         <v>2028</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="D14">
         <v>2029</v>
       </c>
       <c r="E14" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="F14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="D15">
         <v>2026</v>
       </c>
       <c r="F15" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>2028</v>
       </c>
       <c r="E16" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="F16" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
@@ -1702,16 +1660,16 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="D17">
         <v>2029</v>
       </c>
       <c r="E17" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="F17" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -1719,13 +1677,13 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D18">
         <v>2028</v>
       </c>
       <c r="F18" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
@@ -1733,13 +1691,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D19">
         <v>2027</v>
       </c>
       <c r="F19" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
@@ -1747,13 +1705,13 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D20">
         <v>2029</v>
       </c>
       <c r="F20" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
@@ -1761,16 +1719,16 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D21">
         <v>2027</v>
       </c>
       <c r="E21" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F21" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
@@ -1778,16 +1736,16 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>326</v>
       </c>
       <c r="D22">
         <v>2028</v>
       </c>
       <c r="E22" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="F22" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.35">
@@ -1795,13 +1753,13 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="D23">
         <v>2029</v>
       </c>
       <c r="F23" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
@@ -1809,7 +1767,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D24">
         <v>2029</v>
@@ -1820,16 +1778,16 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D25">
         <v>2027</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
@@ -1837,13 +1795,13 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D26">
         <v>2027</v>
       </c>
       <c r="F26" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
@@ -1851,13 +1809,13 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D27">
         <v>2027</v>
       </c>
       <c r="F27" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
@@ -1865,13 +1823,13 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>324</v>
       </c>
       <c r="D28">
         <v>2027</v>
       </c>
       <c r="F28" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.35">
@@ -1879,16 +1837,16 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D29">
         <v>2027</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F29" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.35">
@@ -1896,13 +1854,13 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D30">
         <v>2028</v>
       </c>
       <c r="F30" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
@@ -1910,16 +1868,16 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D31">
         <v>2029</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
@@ -1927,16 +1885,16 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>325</v>
       </c>
       <c r="D32">
         <v>2026</v>
       </c>
       <c r="E32" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="F32" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
@@ -1944,13 +1902,13 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>322</v>
       </c>
       <c r="D33">
         <v>2028</v>
       </c>
       <c r="F33" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -1974,185 +1932,185 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C1" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="D1" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="E1" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="E3" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="D4" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="E4" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="C6" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="C7" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="D7" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="D8" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="D9" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D10" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="D11" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="D12" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="D14" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -2170,952 +2128,952 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="126" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="127" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="128" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="132" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="133" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="134" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="135" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="136" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="137" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
     </row>
     <row r="141" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="142" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
     </row>
     <row r="143" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="146" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
     </row>
     <row r="150" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B151" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B157" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="158" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="160" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
     </row>
     <row r="161" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
     </row>
     <row r="162" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B162" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B163" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="164" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B165" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="166" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="167" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B167" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="168" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B168" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="169" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
     </row>
     <row r="170" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B170" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B172" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="173" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B174" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="178" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="179" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="180" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="181" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="182" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="183" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="184" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="185" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="186" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="188" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="189" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="190" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="191" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
